--- a/Documento 0/Seguimiento_Sprint_Documento0.xlsx
+++ b/Documento 0/Seguimiento_Sprint_Documento0.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Seguimiento_Sprint" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Burn_Up_Down" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Seguimiento_Sprint!$A$3:$M$35</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -21,9 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="152">
-  <si>
-    <t xml:space="preserve">OBJETIVOS: Elaborar y validar el Documento 0 del proyecto, cubriendo la iniciación, el contexto organizacional, el diagnóstico interno y externo (PESTEL, Porter, FODA, cadena de valor, Ishikawa, histograma), el levantamiento de requerimientos, los casos de uso, la estimación de costos/beneficios y la entrega/presentación formal del documento.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="151">
+  <si>
+    <t xml:space="preserve">Seguimiento sprint Documento 0</t>
   </si>
   <si>
     <t xml:space="preserve">PILA DEL PRODUCTO</t>
@@ -35,7 +38,10 @@
     <t xml:space="preserve">PROYECTO</t>
   </si>
   <si>
-    <t xml:space="preserve">Verficación</t>
+    <t xml:space="preserve">Verificación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incremento</t>
   </si>
   <si>
     <t xml:space="preserve">Prioridad</t>
@@ -74,6 +80,9 @@
     <t xml:space="preserve">Detalles</t>
   </si>
   <si>
+    <t xml:space="preserve">Documento 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Iniciación</t>
   </si>
   <si>
@@ -86,9 +95,6 @@
     <t xml:space="preserve">24-03-2026  1 H</t>
   </si>
   <si>
-    <t xml:space="preserve">Vicente</t>
-  </si>
-  <si>
     <t xml:space="preserve">OK</t>
   </si>
   <si>
@@ -122,22 +128,23 @@
     <t xml:space="preserve">Construir product backlog</t>
   </si>
   <si>
-    <t xml:space="preserve">27-03-2026  1.5 H          30-03-2026  1.5 H          01-04-2026  1 H</t>
+    <t xml:space="preserve">27-03-2026  1.5 H
+30-03-2026  1.5 H
+01-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se construyó el product backlog inicial del proyecto, priorizando las funcionalidades a desarrollar. Entregable: product backlog priorizado. Criterio de aceptación: ítems priorizados y estimados a nivel general; evidencia: backlog incorporado a la planificación del proyecto.</t>
   </si>
   <si>
-    <t xml:space="preserve">Documento 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Introducción</t>
   </si>
   <si>
     <t xml:space="preserve">Paulina Urrutia Moya</t>
   </si>
   <si>
-    <t xml:space="preserve">21-03-2026  1 H          23-03-2026  1 H          25-03-2026  1 H</t>
+    <t xml:space="preserve">21-03-2026  1 H
+23-03-2026  1 H
+25-03-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se redactó la introducción del Documento 0, presentando el propósito, alcance y estructura del informe. Entregable: sección de introducción. Criterio de aceptación: propósito y alcance del documento claramente expuestos; evidencia: sección integrada al Documento 0.</t>
@@ -155,10 +162,12 @@
     <t xml:space="preserve">Problema</t>
   </si>
   <si>
-    <t xml:space="preserve">Benjamin Parraguez Aguirre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28-03-2026  1 H          31-03-2026  1 H          03-04-2026  1 H</t>
+    <t xml:space="preserve">Benjamín Parraguez Aguirre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-03-2026  1 H
+31-03-2026  1 H
+03-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se identificó y describió la problemática que da origen al proyecto. Entregable: sección de descripción de la problemática. Criterio de aceptación: problemática claramente definida y justificada; evidencia: sección integrada al Documento 0.</t>
@@ -167,7 +176,8 @@
     <t xml:space="preserve">Objetivo General</t>
   </si>
   <si>
-    <t xml:space="preserve">27-03-2026  1 H          05-04-2026  1 H</t>
+    <t xml:space="preserve">27-03-2026  1 H
+05-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se redactó el objetivo general del proyecto en base a la problemática identificada. Entregable: objetivo general. Criterio de aceptación: objetivo medible y alineado con la problemática; evidencia: sección integrada al Documento 0.</t>
@@ -176,7 +186,8 @@
     <t xml:space="preserve">Objetivos Específicos</t>
   </si>
   <si>
-    <t xml:space="preserve">28-03-2026  1 H          05-04-2026  1 H</t>
+    <t xml:space="preserve">28-03-2026  1 H
+05-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se definieron los objetivos específicos derivados del objetivo general del proyecto. Entregable: listado de objetivos específicos. Criterio de aceptación: objetivos medibles y consistentes con el objetivo general; evidencia: sección integrada al Documento 0.</t>
@@ -185,7 +196,8 @@
     <t xml:space="preserve">Organigramas</t>
   </si>
   <si>
-    <t xml:space="preserve">26-03-2026  1 H          01-04-2026  1 H</t>
+    <t xml:space="preserve">26-03-2026  1 H
+01-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se elaboraron los organigramas de la empresa representando su estructura jerárquica y funcional. Entregable: organigramas de la organización. Criterio de aceptación: estructura organizacional representada correctamente; evidencia: diagramas incorporados al Documento 0.</t>
@@ -197,7 +209,8 @@
     <t xml:space="preserve">Preparar la Entrevista del Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">22-03-2026  1 H          23-03-2026  1 H</t>
+    <t xml:space="preserve">22-03-2026  1 H
+23-03-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se prepararon las preguntas y la pauta de la entrevista a realizar al usuario/cliente. Entregable: pauta de entrevista. Criterio de aceptación: preguntas alineadas con los objetivos del levantamiento; evidencia: pauta utilizada en la primera entrevista.</t>
@@ -209,7 +222,9 @@
     <t xml:space="preserve">PEST o PESTEL</t>
   </si>
   <si>
-    <t xml:space="preserve">31-03-2026  1 H          02-04-2026  1 H          05-04-2026  1 H</t>
+    <t xml:space="preserve">31-03-2026  1 H
+02-04-2026  1 H
+05-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se desarrolló el análisis PESTEL de factores políticos, económicos, sociales, tecnológicos, ecológicos y legales que afectan a la organización. Entregable: análisis PESTEL. Criterio de aceptación: factores externos identificados y justificados; evidencia: sección integrada al Documento 0.</t>
@@ -218,7 +233,7 @@
     <t xml:space="preserve">Primera Entrevista Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">Vicente Ortega Nobizelli, Tomás Hurtado Silva, Benjamin Parraguez Aguirre</t>
+    <t xml:space="preserve">Vicente Ortega Nobizelli, Tomás Hurtado Silva, Benjamín Parraguez Aguirre</t>
   </si>
   <si>
     <t xml:space="preserve">24-03-2026  3 H</t>
@@ -242,7 +257,8 @@
     <t xml:space="preserve">Cadena de valor</t>
   </si>
   <si>
-    <t xml:space="preserve">30-03-2026  1 H          01-04-2026  1 H</t>
+    <t xml:space="preserve">30-03-2026  1 H
+01-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se construyó la cadena de valor de la organización identificando actividades primarias y de apoyo. Entregable: cadena de valor. Criterio de aceptación: actividades correctamente clasificadas; evidencia: diagrama incorporado al Documento 0.</t>
@@ -269,7 +285,9 @@
     <t xml:space="preserve">Diego Carabajal Belmar</t>
   </si>
   <si>
-    <t xml:space="preserve">22-03-2026  1 H          25-03-2026  1 H          27-03-2026  1 H</t>
+    <t xml:space="preserve">22-03-2026  1 H
+25-03-2026  1 H
+27-03-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se elaboró el diagrama de Ishikawa para identificar las causas raíz de la problemática detectada. Entregable: diagrama de Ishikawa. Criterio de aceptación: causas identificadas y clasificadas coherentemente; evidencia: diagrama integrado al análisis cualitativo del Documento 0.</t>
@@ -284,7 +302,8 @@
     <t xml:space="preserve">Diego Sepúlveda Solar, Vicente Ortega Nobizelli</t>
   </si>
   <si>
-    <t xml:space="preserve">04-04-2026  1 H          06-04-2026  2 H</t>
+    <t xml:space="preserve">04-04-2026  1 H
+06-04-2026  2 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se modelaron en Bizagi los procesos generales de la organización (manufactura, ensamble, transporte y despacho). Entregable: diagramas de procesos en Bizagi. Criterio de aceptación: procesos modelados de forma completa y coherente con la operación real; evidencia: diagramas incorporados al Documento 0.</t>
@@ -293,7 +312,8 @@
     <t xml:space="preserve">Porter</t>
   </si>
   <si>
-    <t xml:space="preserve">04-04-2026  1 H          05-04-2026  1 H</t>
+    <t xml:space="preserve">04-04-2026  1 H
+05-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se desarrolló el análisis de las 5 fuerzas de Porter para evaluar la posición competitiva de la organización. Entregable: análisis de Porter. Criterio de aceptación: las cinco fuerzas analizadas y justificadas; evidencia: sección integrada al Documento 0.</t>
@@ -320,7 +340,10 @@
     <t xml:space="preserve">Paulina Urrutia Moya, Tomás Hurtado Silva</t>
   </si>
   <si>
-    <t xml:space="preserve">21-03-2026  2 H          31-03-2026  2 H          08-04-2026  2 H          15-04-2026  2 H</t>
+    <t xml:space="preserve">21-03-2026  2 H
+31-03-2026  2 H
+08-04-2026  2 H
+15-04-2026  2 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se relevaron los requerimientos del usuario a través de entrevistas y revisión documental, consolidando la información recabada. Entregable: listado preliminar de requerimientos. Criterio de aceptación: requerimientos identificados, redactados y validados con el cliente; evidencia: registro de requerimientos levantados.</t>
@@ -341,7 +364,9 @@
     <t xml:space="preserve">Tomás Hurtado Silva, Paulina Urrutia Moya</t>
   </si>
   <si>
-    <t xml:space="preserve">17-03-2026  2 H          01-04-2026  2 H          17-04-2026  2 H</t>
+    <t xml:space="preserve">17-03-2026  2 H
+01-04-2026  2 H
+17-04-2026  2 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se estructuraron los requerimientos funcionales bajo el estándar ESA (User Requirements). Entregable: requerimientos funcionales en formato UR. Criterio de aceptación: requerimientos redactados según el estándar y trazables; evidencia: sección de requerimientos integrada al Documento 0.</t>
@@ -353,7 +378,9 @@
     <t xml:space="preserve">Diagrama de casos de uso</t>
   </si>
   <si>
-    <t xml:space="preserve">31-03-2026  1.5 H          10-04-2026  2 H          18-04-2026  1.5 H</t>
+    <t xml:space="preserve">31-03-2026  1.5 H
+10-04-2026  2 H
+18-04-2026  1.5 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se elaboró el diagrama de casos de uso general del sistema en base a los requerimientos levantados. Entregable: diagrama de casos de uso. Criterio de aceptación: actores y casos de uso correctamente representados; evidencia: diagrama incorporado al Documento 0.</t>
@@ -362,7 +389,9 @@
     <t xml:space="preserve">Casos de uso Extendido</t>
   </si>
   <si>
-    <t xml:space="preserve">01-04-2026  2 H          08-04-2026  1.5 H          15-04-2026  1.5 H</t>
+    <t xml:space="preserve">01-04-2026  2 H
+08-04-2026  1.5 H
+15-04-2026  1.5 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se documentaron los casos de uso extendidos, describiendo flujo principal, flujos alternativos y precondiciones. Entregable: descripciones extendidas de casos de uso. Criterio de aceptación: casos de uso completos y trazables con los requerimientos; evidencia: sección integrada al Documento 0.</t>
@@ -374,7 +403,8 @@
     <t xml:space="preserve">Estimación de costos y beneficios</t>
   </si>
   <si>
-    <t xml:space="preserve">11-04-2026  1.5 H          17-04-2026  1.5 H</t>
+    <t xml:space="preserve">11-04-2026  1.5 H
+17-04-2026  1.5 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se estimaron los costos y beneficios asociados al desarrollo del proyecto. Entregable: estimación de costos y beneficios. Criterio de aceptación: cifras justificadas y coherentes con el alcance definido; evidencia: sección integrada al Documento 0.</t>
@@ -386,10 +416,8 @@
     <t xml:space="preserve">Matriz de requerimientos v/s casos de uso</t>
   </si>
   <si>
-    <t xml:space="preserve">Paulina Urrutia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01-04-2026  1 H          18-04-2026  2 H</t>
+    <t xml:space="preserve">01-04-2026  1 H
+18-04-2026  2 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se elaboró la matriz de trazabilidad entre los requerimientos y los casos de uso definidos. Entregable: matriz de requerimientos vs casos de uso. Criterio de aceptación: todos los requerimientos asociados a al menos un caso de uso; evidencia: matriz incorporada al Documento 0.</t>
@@ -413,7 +441,8 @@
     <t xml:space="preserve">Correcciones Documento 0</t>
   </si>
   <si>
-    <t xml:space="preserve">16-04-2026  1 H          19-04-2026  2 H</t>
+    <t xml:space="preserve">16-04-2026  1 H
+19-04-2026  2 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se aplicaron las correcciones identificadas en la revisión del Documento 0. Entregable: Documento 0 corregido. Criterio de aceptación: observaciones resueltas en su totalidad; evidencia: documento actualizado con cambios trazables.</t>
@@ -431,7 +460,8 @@
     <t xml:space="preserve">Preparación Presentación</t>
   </si>
   <si>
-    <t xml:space="preserve">20-04-2026  1 H          21-04-2026  1 H</t>
+    <t xml:space="preserve">20-04-2026  1 H
+21-04-2026  1 H</t>
   </si>
   <si>
     <t xml:space="preserve">Se preparó la presentación oral del Documento 0, incluyendo diapositivas y distribución de temas por integrante. Entregable: presentación preparada. Criterio de aceptación: contenido resumido y roles de exposición asignados; evidencia: material de presentación.</t>
@@ -446,10 +476,10 @@
     <t xml:space="preserve">Se realizó la presentación oral del Documento 0 ante el profesor guía. Entregable: presentación realizada. Criterio de aceptación: exposición completa dentro del tiempo asignado; evidencia: registro/retroalimentación de la presentación.</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguimiento Burn-Up / Burn-Down — Desarrollo Documento 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente: hoja "Seguimiento_Sprint" (columnas Estimar HH y Registro Diario en Horas). HH Estimada diaria = Estimar HH de cada tarea repartido en partes iguales entre sus días de registro.</t>
+    <t xml:space="preserve">Seguimiento Burn-Up / Burn-Down — Documento 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente: hoja "Seguimiento_Sprint" (filas del Documento 0; columnas Estimar HH y Registro Diario en Horas). HH Estimada diaria = Estimar HH de cada tarea repartido en partes iguales entre sus días de registro.</t>
   </si>
   <si>
     <t xml:space="preserve">Día</t>
@@ -483,12 +513,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -524,16 +552,21 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -545,19 +578,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF1F4E78"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -565,20 +590,22 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -635,19 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5998"/>
+        <fgColor rgb="FFCCC0D9"/>
         <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7998"/>
+        <fgColor rgb="FFDAEEF3"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5998"/>
+        <fgColor rgb="FFD6E3BC"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
@@ -714,7 +741,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -727,23 +754,19 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -751,51 +774,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -811,7 +814,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -819,11 +822,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -836,6 +839,39 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDAEEF3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD6E3BC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -857,11 +893,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFDBEEF4"/>
+      <rgbColor rgb="FFDAEEF3"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF1F77B4"/>
-      <rgbColor rgb="FFCCC1DA"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCC0D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -872,7 +908,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9D9D9"/>
-      <rgbColor rgb="FFD7E4BD"/>
+      <rgbColor rgb="FFD6E3BC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF9BC2E6"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -883,14 +919,14 @@
       <rgbColor rgb="FFA9D08E"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FFB3B3B3"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFD62728"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
@@ -927,7 +963,7 @@
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
-              <a:t>Gráfica Burn-Up — Incremento 2</a:t>
+              <a:t>Gráfica Burn-Up — Documento 0</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -950,22 +986,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"HH Estimada"</c:f>
+              <c:f>Burn_Up_Down!E4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HH Estimada</c:v>
+                  <c:v>HH Estimada (acum.)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1f77b4"/>
+              <a:srgbClr val="1f4e78"/>
             </a:solidFill>
-            <a:ln w="20160">
+            <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="1f77b4"/>
+                <a:srgbClr val="1f4e78"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -975,27 +1011,22 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1005,9 +1036,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Burn_Up_Down!$A$5:$A$36</c:f>
+              <c:f>Burn_Up_Down!$A$5:$A$41</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1103,16 +1134,31 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Burn_Up_Down!$E$5:$E$36</c:f>
+              <c:f>Burn_Up_Down!$E$5:$E$41</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1144,40 +1190,40 @@
                   <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>27.3333</c:v>
+                  <c:v>27.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>29.3333</c:v>
+                  <c:v>29.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29.3333</c:v>
+                  <c:v>29.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>31.6666</c:v>
+                  <c:v>31.6666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>39.3333</c:v>
+                  <c:v>39.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>47.8333</c:v>
+                  <c:v>47.8333333333</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.8333</c:v>
+                  <c:v>48.8333333333</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>49.8333</c:v>
+                  <c:v>49.8333333333</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>52.3333</c:v>
+                  <c:v>52.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>56.3333</c:v>
+                  <c:v>56.3333333333</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>58.8333</c:v>
+                  <c:v>58.8333333333</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>58.8333</c:v>
+                  <c:v>58.8333333333</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>63.5</c:v>
@@ -1186,28 +1232,43 @@
                   <c:v>63.5</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>65.1667</c:v>
+                  <c:v>65.1666666667</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>66.6667</c:v>
+                  <c:v>66.6666666667</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>66.6667</c:v>
+                  <c:v>66.6666666667</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>66.6667</c:v>
+                  <c:v>66.6666666667</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>66.6667</c:v>
+                  <c:v>66.6666666667</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>70.3334</c:v>
+                  <c:v>70.3333333334</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>73.8334</c:v>
+                  <c:v>73.8333333334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>77.3334</c:v>
+                  <c:v>77.3333333334</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>80.5000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>83.0000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>84.0000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85.0000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>86.0000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1219,22 +1280,22 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"HH Efectiva"</c:f>
+              <c:f>Burn_Up_Down!F4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HH Efectiva</c:v>
+                  <c:v>HH Efectiva (acum.)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="d62728"/>
+              <a:srgbClr val="ed7d31"/>
             </a:solidFill>
-            <a:ln w="20160">
+            <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="d62728"/>
+                <a:srgbClr val="ed7d31"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1244,27 +1305,22 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1274,9 +1330,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Burn_Up_Down!$A$5:$A$36</c:f>
+              <c:f>Burn_Up_Down!$A$5:$A$41</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1372,16 +1428,31 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Burn_Up_Down!$F$5:$F$36</c:f>
+              <c:f>Burn_Up_Down!$F$5:$F$41</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -1477,6 +1548,21 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>76.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1491,11 +1577,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="45141421"/>
-        <c:axId val="84502754"/>
+        <c:axId val="53600515"/>
+        <c:axId val="44857369"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="45141421"/>
+        <c:axId val="53600515"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1537,7 +1623,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1563,7 +1649,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84502754"/>
+        <c:crossAx val="44857369"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1571,7 +1657,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84502754"/>
+        <c:axId val="44857369"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1622,7 +1708,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1648,7 +1734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45141421"/>
+        <c:crossAx val="53600515"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1660,7 +1746,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1729,7 +1815,7 @@
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
-              <a:t>Gráfica Burn-Down — Incremento 2</a:t>
+              <a:t>Gráfica Burn-Down — Documento 0</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1752,22 +1838,22 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>"HH Estimada"</c:f>
+              <c:f>Burn_Up_Down!G4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HH Estimada</c:v>
+                  <c:v>Remanente Estimada</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1f77b4"/>
+              <a:srgbClr val="1f4e78"/>
             </a:solidFill>
-            <a:ln w="20160">
+            <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="1f77b4"/>
+                <a:srgbClr val="1f4e78"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1777,27 +1863,22 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1807,9 +1888,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Burn_Up_Down!$A$5:$A$36</c:f>
+              <c:f>Burn_Up_Down!$A$5:$A$41</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1905,16 +1986,31 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Burn_Up_Down!$G$5:$G$36</c:f>
+              <c:f>Burn_Up_Down!$G$5:$G$41</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>84</c:v>
                 </c:pt>
@@ -1955,7 +2051,7 @@
                   <c:v>56.6667</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54.3334</c:v>
+                  <c:v>54.3333</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>46.6667</c:v>
@@ -2003,13 +2099,28 @@
                   <c:v>19.3333</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>15.6666</c:v>
+                  <c:v>15.6667</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>12.1666</c:v>
+                  <c:v>12.1667</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8.66659999999999</c:v>
+                  <c:v>8.6667</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2021,22 +2132,22 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>"HH Efectiva"</c:f>
+              <c:f>Burn_Up_Down!H4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>HH Efectiva</c:v>
+                  <c:v>Remanente Efectiva</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="d62728"/>
+              <a:srgbClr val="ed7d31"/>
             </a:solidFill>
-            <a:ln w="20160">
+            <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="d62728"/>
+                <a:srgbClr val="ed7d31"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2046,27 +2157,22 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="square"/>
+              <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
                     <a:latin typeface="Arial"/>
-                    <a:ea typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
+            <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -2076,9 +2182,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Burn_Up_Down!$A$5:$A$36</c:f>
+              <c:f>Burn_Up_Down!$A$5:$A$41</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -2174,16 +2280,31 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Burn_Up_Down!$H$5:$H$36</c:f>
+              <c:f>Burn_Up_Down!$H$5:$H$41</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="37"/>
                 <c:pt idx="0">
                   <c:v>84</c:v>
                 </c:pt>
@@ -2279,6 +2400,21 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2293,11 +2429,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="35131013"/>
-        <c:axId val="77154599"/>
+        <c:axId val="48606810"/>
+        <c:axId val="86328491"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="35131013"/>
+        <c:axId val="48606810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2339,7 +2475,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2365,7 +2501,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77154599"/>
+        <c:crossAx val="86328491"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2373,7 +2509,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77154599"/>
+        <c:axId val="86328491"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2424,7 +2560,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2450,7 +2586,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35131013"/>
+        <c:crossAx val="48606810"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2462,7 +2598,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2504,19 +2640,23 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>291600</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>699840</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2524,8 +2664,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="7229880"/>
-        <a:ext cx="7199280" cy="3239280"/>
+        <a:off x="0" y="8429760"/>
+        <a:ext cx="6479640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2539,14 +2679,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>522360</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>398880</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2554,8 +2694,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8246880" y="7229880"/>
-        <a:ext cx="7199280" cy="3239280"/>
+        <a:off x="8246880" y="8429760"/>
+        <a:ext cx="6479640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2569,9 +2709,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -2579,10 +2719,10 @@
         <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4f81bd"/>
@@ -2606,10 +2746,10 @@
         <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="0000ff"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
@@ -2626,22 +2766,67 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2659,46 +2844,34 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:shade val="63000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -2712,23 +2885,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M1048576"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="58.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="14" style="1" width="9.1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2740,1292 +2915,1437 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="7" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+      <c r="M3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>46105</v>
+      <c r="G4" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>46105</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="11" t="n">
+        <v>46105</v>
+      </c>
+      <c r="J4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+      <c r="M4" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" s="9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>46106</v>
+      <c r="G5" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>46106</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="11" t="n">
+        <v>46106</v>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="L5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>46108</v>
+      <c r="G6" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="H6" s="11" t="n">
         <v>46108</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="11" t="n">
+        <v>46108</v>
+      </c>
+      <c r="J6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="K6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="L6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="11" t="n">
         <v>46108</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="I7" s="11" t="n">
         <v>46113</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="J7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="K7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="103.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="L7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="C8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="F8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="H8" s="11" t="n">
         <v>46102</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="I8" s="11" t="n">
         <v>46106</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="J8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="K8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+    <row r="9" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="C9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="H9" s="11" t="n">
         <v>46102</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="I9" s="11" t="n">
         <v>46106</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="J9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="96.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
+    <row r="10" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="F10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="H10" s="11" t="n">
         <v>46109</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="I10" s="11" t="n">
         <v>46115</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="J10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="K10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="99" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
+    <row r="11" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="C11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="F11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="H11" s="11" t="n">
         <v>46108</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="I11" s="11" t="n">
         <v>46117</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="J11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="K11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
+    <row r="12" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="C12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="G12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>46109</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="I12" s="11" t="n">
         <v>46117</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="J12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="K12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="75.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
+    <row r="13" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="F13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="G13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="H13" s="11" t="n">
         <v>46107</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="I13" s="11" t="n">
         <v>46113</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="J13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="K13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="10" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="76.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="n">
+    <row r="14" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="G14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="11" t="n">
+      <c r="H14" s="11" t="n">
         <v>46103</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="I14" s="11" t="n">
         <v>46104</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="J14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="K14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="111" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
+    <row r="15" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="F15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="G15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="H15" s="11" t="n">
         <v>46112</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="I15" s="11" t="n">
         <v>46117</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="J15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="14" t="s">
+      <c r="L15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="n">
+    <row r="16" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="D16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="F16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="G16" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>46105</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>46105</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="11" t="n">
+        <v>46105</v>
+      </c>
+      <c r="J16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="K16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="106.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="n">
+    <row r="17" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="D17" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="F17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>46106</v>
+      <c r="G17" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>46106</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="11" t="n">
+        <v>46106</v>
+      </c>
+      <c r="J17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="K17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="n">
+    <row r="18" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="F18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="G18" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="H18" s="11" t="n">
         <v>46111</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="I18" s="11" t="n">
         <v>46113</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="J18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="K18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="107.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="n">
+    <row r="19" customFormat="false" ht="96" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="G19" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>46112</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>46112</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="11" t="n">
+        <v>46112</v>
+      </c>
+      <c r="J19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="K19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="n">
+    <row r="20" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="F20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="G20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="H20" s="11" t="n">
         <v>46103</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="I20" s="11" t="n">
         <v>46108</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="J20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="K20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="107.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
+    <row r="21" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="F21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="G21" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="H21" s="11" t="n">
         <v>46116</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="I21" s="11" t="n">
         <v>46118</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="J21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="K21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="14" t="s">
+      <c r="L21" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="n">
+    <row r="22" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="F22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="G22" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="H22" s="11" t="n">
         <v>46116</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="I22" s="11" t="n">
         <v>46117</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="J22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="K22" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="14" t="s">
+      <c r="L22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="10" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="n">
+    <row r="23" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="C23" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="F23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="G23" s="10" t="s">
         <v>94</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>46118</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>46118</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="11" t="n">
+        <v>46118</v>
+      </c>
+      <c r="J23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="K23" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M23" s="10" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="n">
+    <row r="24" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="F24" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="G24" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="H24" s="11" t="n">
         <v>46102</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="I24" s="11" t="n">
         <v>46127</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="J24" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="K24" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K24" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="10" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="n">
+    <row r="25" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="C25" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="G25" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>46120</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>46120</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="11" t="n">
+        <v>46120</v>
+      </c>
+      <c r="J25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="K25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K25" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="14" t="s">
+      <c r="L25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="n">
+    <row r="26" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="F26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="G26" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="H26" s="11" t="n">
         <v>46098</v>
       </c>
-      <c r="H26" s="11" t="n">
+      <c r="I26" s="11" t="n">
         <v>46129</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="J26" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="K26" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K26" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="10" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="82.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="n">
+    <row r="27" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="G27" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="H27" s="11" t="n">
         <v>46112</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="I27" s="11" t="n">
         <v>46130</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="J27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K27" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="139.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="n">
+    <row r="28" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="D28" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="F28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="G28" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="H28" s="11" t="n">
         <v>46113</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="I28" s="11" t="n">
         <v>46127</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="J28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="K28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K28" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="n">
+    <row r="29" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="C29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="D29" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="F29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="H29" s="11" t="n">
         <v>46123</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="I29" s="11" t="n">
         <v>46129</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="J29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="K29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K29" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L29" s="14" t="s">
+      <c r="L29" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="n">
+    <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="C30" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="E30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="H30" s="11" t="n">
+        <v>46113</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>46130</v>
+      </c>
+      <c r="J30" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="K30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M30" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="11" t="n">
-        <v>46113</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>46130</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L30" s="14" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="F31" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G31" s="11" t="n">
-        <v>46128</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>46128</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="11" t="n">
+        <v>46128</v>
+      </c>
+      <c r="J31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="K31" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="n">
+      <c r="E32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>46128</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B32" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="G32" s="11" t="n">
-        <v>46128</v>
-      </c>
-      <c r="H32" s="11" t="n">
-        <v>46131</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="12" t="s">
+      <c r="C33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K32" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="n">
+      <c r="F33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="9" t="s">
+      <c r="G33" s="10" t="s">
         <v>132</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>46131</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>46131</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="11" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="n">
+      <c r="E34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>46132</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>46133</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G34" s="11" t="n">
-        <v>46132</v>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>46133</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L34" s="14" t="s">
+      <c r="C35" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="n">
+      <c r="E35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="9" t="s">
+      <c r="G35" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="G35" s="11" t="n">
-        <v>46134</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>46134</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="I35" s="11" t="n">
+        <v>46134</v>
+      </c>
+      <c r="J35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="K35" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K35" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>140</v>
-      </c>
-    </row>
+      <c r="L35" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <autoFilter ref="A3:M35"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4034,6 +4354,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4042,8 +4363,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -4051,1175 +4372,2206 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="12" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="B4" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="D4" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="E4" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="F4" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="G4" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="H4" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="I4" s="14"/>
+      <c r="J4" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="24" t="n">
-        <f aca="false">SUM(Seguimiento_Sprint!E4:E35)</f>
+      <c r="K4" s="18" t="n">
+        <f aca="false">SUM(Seguimiento_Sprint!F4:F35)</f>
         <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="20" t="n">
         <v>46098</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="21" t="n">
         <f aca="false">C5</f>
         <v>2</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="21" t="n">
         <f aca="false">D5</f>
         <v>2</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <f aca="false">$K$4-E5</f>
+      <c r="G5" s="21" t="n">
+        <f aca="false">ROUND($K$4-E5,4)</f>
         <v>84</v>
       </c>
-      <c r="H5" s="27" t="n">
-        <f aca="false">$K$4-F5</f>
+      <c r="H5" s="21" t="n">
+        <f aca="false">ROUND($K$4-F5,4)</f>
         <v>84</v>
       </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="20" t="n">
         <v>46099</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">E5+C6</f>
         <v>2</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="21" t="n">
         <f aca="false">F5+D6</f>
         <v>2</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <f aca="false">$K$4-E6</f>
+      <c r="G6" s="21" t="n">
+        <f aca="false">ROUND($K$4-E6,4)</f>
         <v>84</v>
       </c>
-      <c r="H6" s="27" t="n">
-        <f aca="false">$K$4-F6</f>
+      <c r="H6" s="21" t="n">
+        <f aca="false">ROUND($K$4-F6,4)</f>
         <v>84</v>
       </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="20" t="n">
         <v>46100</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">E6+C7</f>
         <v>2</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="21" t="n">
         <f aca="false">F6+D7</f>
         <v>2</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <f aca="false">$K$4-E7</f>
+      <c r="G7" s="21" t="n">
+        <f aca="false">ROUND($K$4-E7,4)</f>
         <v>84</v>
       </c>
-      <c r="H7" s="27" t="n">
-        <f aca="false">$K$4-F7</f>
+      <c r="H7" s="21" t="n">
+        <f aca="false">ROUND($K$4-F7,4)</f>
         <v>84</v>
       </c>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="20" t="n">
         <v>46101</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="21" t="n">
         <f aca="false">E7+C8</f>
         <v>2</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="21" t="n">
         <f aca="false">F7+D8</f>
         <v>2</v>
       </c>
-      <c r="G8" s="27" t="n">
-        <f aca="false">$K$4-E8</f>
+      <c r="G8" s="21" t="n">
+        <f aca="false">ROUND($K$4-E8,4)</f>
         <v>84</v>
       </c>
-      <c r="H8" s="27" t="n">
-        <f aca="false">$K$4-F8</f>
+      <c r="H8" s="21" t="n">
+        <f aca="false">ROUND($K$4-F8,4)</f>
         <v>84</v>
       </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="20" t="n">
         <v>46102</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">E8+C9</f>
         <v>6</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">F8+D9</f>
         <v>6</v>
       </c>
-      <c r="G9" s="27" t="n">
-        <f aca="false">$K$4-E9</f>
+      <c r="G9" s="21" t="n">
+        <f aca="false">ROUND($K$4-E9,4)</f>
         <v>80</v>
       </c>
-      <c r="H9" s="27" t="n">
-        <f aca="false">$K$4-F9</f>
+      <c r="H9" s="21" t="n">
+        <f aca="false">ROUND($K$4-F9,4)</f>
         <v>80</v>
       </c>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="20" t="n">
         <v>46103</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">E9+C10</f>
         <v>8</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="21" t="n">
         <f aca="false">F9+D10</f>
         <v>8</v>
       </c>
-      <c r="G10" s="27" t="n">
-        <f aca="false">$K$4-E10</f>
+      <c r="G10" s="21" t="n">
+        <f aca="false">ROUND($K$4-E10,4)</f>
         <v>78</v>
       </c>
-      <c r="H10" s="27" t="n">
-        <f aca="false">$K$4-F10</f>
+      <c r="H10" s="21" t="n">
+        <f aca="false">ROUND($K$4-F10,4)</f>
         <v>78</v>
       </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="20" t="n">
         <v>46104</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">E10+C11</f>
         <v>11</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="21" t="n">
         <f aca="false">F10+D11</f>
         <v>11</v>
       </c>
-      <c r="G11" s="27" t="n">
-        <f aca="false">$K$4-E11</f>
+      <c r="G11" s="21" t="n">
+        <f aca="false">ROUND($K$4-E11,4)</f>
         <v>75</v>
       </c>
-      <c r="H11" s="27" t="n">
-        <f aca="false">$K$4-F11</f>
+      <c r="H11" s="21" t="n">
+        <f aca="false">ROUND($K$4-F11,4)</f>
         <v>75</v>
       </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="20" t="n">
         <v>46105</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">E11+C12</f>
         <v>15</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="21" t="n">
         <f aca="false">F11+D12</f>
         <v>15</v>
       </c>
-      <c r="G12" s="27" t="n">
-        <f aca="false">$K$4-E12</f>
+      <c r="G12" s="21" t="n">
+        <f aca="false">ROUND($K$4-E12,4)</f>
         <v>71</v>
       </c>
-      <c r="H12" s="27" t="n">
-        <f aca="false">$K$4-F12</f>
+      <c r="H12" s="21" t="n">
+        <f aca="false">ROUND($K$4-F12,4)</f>
         <v>71</v>
       </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="20" t="n">
         <v>46106</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="21" t="n">
         <f aca="false">E12+C13</f>
         <v>22</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="21" t="n">
         <f aca="false">F12+D13</f>
         <v>22</v>
       </c>
-      <c r="G13" s="27" t="n">
-        <f aca="false">$K$4-E13</f>
+      <c r="G13" s="21" t="n">
+        <f aca="false">ROUND($K$4-E13,4)</f>
         <v>64</v>
       </c>
-      <c r="H13" s="27" t="n">
-        <f aca="false">$K$4-F13</f>
+      <c r="H13" s="21" t="n">
+        <f aca="false">ROUND($K$4-F13,4)</f>
         <v>64</v>
       </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="20" t="n">
         <v>46107</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">E13+C14</f>
         <v>23</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="21" t="n">
         <f aca="false">F13+D14</f>
         <v>23</v>
       </c>
-      <c r="G14" s="27" t="n">
-        <f aca="false">$K$4-E14</f>
+      <c r="G14" s="21" t="n">
+        <f aca="false">ROUND($K$4-E14,4)</f>
         <v>63</v>
       </c>
-      <c r="H14" s="27" t="n">
-        <f aca="false">$K$4-F14</f>
+      <c r="H14" s="21" t="n">
+        <f aca="false">ROUND($K$4-F14,4)</f>
         <v>63</v>
       </c>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="20" t="n">
         <v>46108</v>
       </c>
-      <c r="C15" s="27" t="n">
-        <v>4.3333</v>
-      </c>
-      <c r="D15" s="27" t="n">
+      <c r="C15" s="21" t="n">
+        <v>4.3333333333</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>4.5</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="21" t="n">
         <f aca="false">E14+C15</f>
-        <v>27.3333</v>
-      </c>
-      <c r="F15" s="27" t="n">
+        <v>27.3333333333</v>
+      </c>
+      <c r="F15" s="21" t="n">
         <f aca="false">F14+D15</f>
         <v>27.5</v>
       </c>
-      <c r="G15" s="27" t="n">
-        <f aca="false">$K$4-E15</f>
+      <c r="G15" s="21" t="n">
+        <f aca="false">ROUND($K$4-E15,4)</f>
         <v>58.6667</v>
       </c>
-      <c r="H15" s="27" t="n">
-        <f aca="false">$K$4-F15</f>
+      <c r="H15" s="21" t="n">
+        <f aca="false">ROUND($K$4-F15,4)</f>
         <v>58.5</v>
       </c>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="20" t="n">
         <v>46109</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="21" t="n">
         <f aca="false">E15+C16</f>
-        <v>29.3333</v>
-      </c>
-      <c r="F16" s="27" t="n">
+        <v>29.3333333333</v>
+      </c>
+      <c r="F16" s="21" t="n">
         <f aca="false">F15+D16</f>
         <v>29.5</v>
       </c>
-      <c r="G16" s="27" t="n">
-        <f aca="false">$K$4-E16</f>
+      <c r="G16" s="21" t="n">
+        <f aca="false">ROUND($K$4-E16,4)</f>
         <v>56.6667</v>
       </c>
-      <c r="H16" s="27" t="n">
-        <f aca="false">$K$4-F16</f>
+      <c r="H16" s="21" t="n">
+        <f aca="false">ROUND($K$4-F16,4)</f>
         <v>56.5</v>
       </c>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="20" t="n">
         <v>46110</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="21" t="n">
         <f aca="false">E16+C17</f>
-        <v>29.3333</v>
-      </c>
-      <c r="F17" s="27" t="n">
+        <v>29.3333333333</v>
+      </c>
+      <c r="F17" s="21" t="n">
         <f aca="false">F16+D17</f>
         <v>29.5</v>
       </c>
-      <c r="G17" s="27" t="n">
-        <f aca="false">$K$4-E17</f>
+      <c r="G17" s="21" t="n">
+        <f aca="false">ROUND($K$4-E17,4)</f>
         <v>56.6667</v>
       </c>
-      <c r="H17" s="27" t="n">
-        <f aca="false">$K$4-F17</f>
+      <c r="H17" s="21" t="n">
+        <f aca="false">ROUND($K$4-F17,4)</f>
         <v>56.5</v>
       </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="20" t="n">
         <v>46111</v>
       </c>
-      <c r="C18" s="27" t="n">
-        <v>2.3333</v>
-      </c>
-      <c r="D18" s="27" t="n">
+      <c r="C18" s="21" t="n">
+        <v>2.3333333333</v>
+      </c>
+      <c r="D18" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="21" t="n">
         <f aca="false">E17+C18</f>
-        <v>31.6666</v>
-      </c>
-      <c r="F18" s="27" t="n">
+        <v>31.6666666666</v>
+      </c>
+      <c r="F18" s="21" t="n">
         <f aca="false">F17+D18</f>
         <v>32</v>
       </c>
-      <c r="G18" s="27" t="n">
-        <f aca="false">$K$4-E18</f>
-        <v>54.3334</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <f aca="false">$K$4-F18</f>
+      <c r="G18" s="21" t="n">
+        <f aca="false">ROUND($K$4-E18,4)</f>
+        <v>54.3333</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <f aca="false">ROUND($K$4-F18,4)</f>
         <v>54</v>
       </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="20" t="n">
         <v>46112</v>
       </c>
-      <c r="C19" s="27" t="n">
-        <v>7.6667</v>
-      </c>
-      <c r="D19" s="27" t="n">
+      <c r="C19" s="21" t="n">
+        <v>7.6666666667</v>
+      </c>
+      <c r="D19" s="21" t="n">
         <v>7.5</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="21" t="n">
         <f aca="false">E18+C19</f>
-        <v>39.3333</v>
-      </c>
-      <c r="F19" s="27" t="n">
+        <v>39.3333333333</v>
+      </c>
+      <c r="F19" s="21" t="n">
         <f aca="false">F18+D19</f>
         <v>39.5</v>
       </c>
-      <c r="G19" s="27" t="n">
-        <f aca="false">$K$4-E19</f>
+      <c r="G19" s="21" t="n">
+        <f aca="false">ROUND($K$4-E19,4)</f>
         <v>46.6667</v>
       </c>
-      <c r="H19" s="27" t="n">
-        <f aca="false">$K$4-F19</f>
+      <c r="H19" s="21" t="n">
+        <f aca="false">ROUND($K$4-F19,4)</f>
         <v>46.5</v>
       </c>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="20" t="n">
         <v>46113</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="21" t="n">
         <v>8.5</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="21" t="n">
         <f aca="false">E19+C20</f>
-        <v>47.8333</v>
-      </c>
-      <c r="F20" s="27" t="n">
+        <v>47.8333333333</v>
+      </c>
+      <c r="F20" s="21" t="n">
         <f aca="false">F19+D20</f>
         <v>47.5</v>
       </c>
-      <c r="G20" s="27" t="n">
-        <f aca="false">$K$4-E20</f>
+      <c r="G20" s="21" t="n">
+        <f aca="false">ROUND($K$4-E20,4)</f>
         <v>38.1667</v>
       </c>
-      <c r="H20" s="27" t="n">
-        <f aca="false">$K$4-F20</f>
+      <c r="H20" s="21" t="n">
+        <f aca="false">ROUND($K$4-F20,4)</f>
         <v>38.5</v>
       </c>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="20" t="n">
         <v>46114</v>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="21" t="n">
         <f aca="false">E20+C21</f>
-        <v>48.8333</v>
-      </c>
-      <c r="F21" s="27" t="n">
+        <v>48.8333333333</v>
+      </c>
+      <c r="F21" s="21" t="n">
         <f aca="false">F20+D21</f>
         <v>48.5</v>
       </c>
-      <c r="G21" s="27" t="n">
-        <f aca="false">$K$4-E21</f>
+      <c r="G21" s="21" t="n">
+        <f aca="false">ROUND($K$4-E21,4)</f>
         <v>37.1667</v>
       </c>
-      <c r="H21" s="27" t="n">
-        <f aca="false">$K$4-F21</f>
+      <c r="H21" s="21" t="n">
+        <f aca="false">ROUND($K$4-F21,4)</f>
         <v>37.5</v>
       </c>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="20" t="n">
         <v>46115</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="21" t="n">
         <f aca="false">E21+C22</f>
-        <v>49.8333</v>
-      </c>
-      <c r="F22" s="27" t="n">
+        <v>49.8333333333</v>
+      </c>
+      <c r="F22" s="21" t="n">
         <f aca="false">F21+D22</f>
         <v>49.5</v>
       </c>
-      <c r="G22" s="27" t="n">
-        <f aca="false">$K$4-E22</f>
+      <c r="G22" s="21" t="n">
+        <f aca="false">ROUND($K$4-E22,4)</f>
         <v>36.1667</v>
       </c>
-      <c r="H22" s="27" t="n">
-        <f aca="false">$K$4-F22</f>
+      <c r="H22" s="21" t="n">
+        <f aca="false">ROUND($K$4-F22,4)</f>
         <v>36.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="20" t="n">
         <v>46116</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="21" t="n">
         <f aca="false">E22+C23</f>
-        <v>52.3333</v>
-      </c>
-      <c r="F23" s="27" t="n">
+        <v>52.3333333333</v>
+      </c>
+      <c r="F23" s="21" t="n">
         <f aca="false">F22+D23</f>
         <v>51.5</v>
       </c>
-      <c r="G23" s="27" t="n">
-        <f aca="false">$K$4-E23</f>
+      <c r="G23" s="21" t="n">
+        <f aca="false">ROUND($K$4-E23,4)</f>
         <v>33.6667</v>
       </c>
-      <c r="H23" s="27" t="n">
-        <f aca="false">$K$4-F23</f>
+      <c r="H23" s="21" t="n">
+        <f aca="false">ROUND($K$4-F23,4)</f>
         <v>34.5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="20" t="n">
         <v>46117</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="21" t="n">
         <f aca="false">E23+C24</f>
-        <v>56.3333</v>
-      </c>
-      <c r="F24" s="27" t="n">
+        <v>56.3333333333</v>
+      </c>
+      <c r="F24" s="21" t="n">
         <f aca="false">F23+D24</f>
         <v>55.5</v>
       </c>
-      <c r="G24" s="27" t="n">
-        <f aca="false">$K$4-E24</f>
+      <c r="G24" s="21" t="n">
+        <f aca="false">ROUND($K$4-E24,4)</f>
         <v>29.6667</v>
       </c>
-      <c r="H24" s="27" t="n">
-        <f aca="false">$K$4-F24</f>
+      <c r="H24" s="21" t="n">
+        <f aca="false">ROUND($K$4-F24,4)</f>
         <v>30.5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="n">
+      <c r="A25" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="20" t="n">
         <v>46118</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="21" t="n">
         <f aca="false">E24+C25</f>
-        <v>58.8333</v>
-      </c>
-      <c r="F25" s="27" t="n">
+        <v>58.8333333333</v>
+      </c>
+      <c r="F25" s="21" t="n">
         <f aca="false">F24+D25</f>
         <v>58.5</v>
       </c>
-      <c r="G25" s="27" t="n">
-        <f aca="false">$K$4-E25</f>
+      <c r="G25" s="21" t="n">
+        <f aca="false">ROUND($K$4-E25,4)</f>
         <v>27.1667</v>
       </c>
-      <c r="H25" s="27" t="n">
-        <f aca="false">$K$4-F25</f>
+      <c r="H25" s="21" t="n">
+        <f aca="false">ROUND($K$4-F25,4)</f>
         <v>27.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="n">
+      <c r="A26" s="19" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="20" t="n">
         <v>46119</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="21" t="n">
         <f aca="false">E25+C26</f>
-        <v>58.8333</v>
-      </c>
-      <c r="F26" s="27" t="n">
+        <v>58.8333333333</v>
+      </c>
+      <c r="F26" s="21" t="n">
         <f aca="false">F25+D26</f>
         <v>58.5</v>
       </c>
-      <c r="G26" s="27" t="n">
-        <f aca="false">$K$4-E26</f>
+      <c r="G26" s="21" t="n">
+        <f aca="false">ROUND($K$4-E26,4)</f>
         <v>27.1667</v>
       </c>
-      <c r="H26" s="27" t="n">
-        <f aca="false">$K$4-F26</f>
+      <c r="H26" s="21" t="n">
+        <f aca="false">ROUND($K$4-F26,4)</f>
         <v>27.5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="n">
+      <c r="A27" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="20" t="n">
         <v>46120</v>
       </c>
-      <c r="C27" s="27" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="D27" s="27" t="n">
+      <c r="C27" s="21" t="n">
+        <v>4.6666666667</v>
+      </c>
+      <c r="D27" s="21" t="n">
         <v>4.5</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="21" t="n">
         <f aca="false">E26+C27</f>
         <v>63.5</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="21" t="n">
         <f aca="false">F26+D27</f>
         <v>63</v>
       </c>
-      <c r="G27" s="27" t="n">
-        <f aca="false">$K$4-E27</f>
+      <c r="G27" s="21" t="n">
+        <f aca="false">ROUND($K$4-E27,4)</f>
         <v>22.5</v>
       </c>
-      <c r="H27" s="27" t="n">
-        <f aca="false">$K$4-F27</f>
+      <c r="H27" s="21" t="n">
+        <f aca="false">ROUND($K$4-F27,4)</f>
         <v>23</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="n">
+      <c r="A28" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="20" t="n">
         <v>46121</v>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="21" t="n">
         <f aca="false">E27+C28</f>
         <v>63.5</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="21" t="n">
         <f aca="false">F27+D28</f>
         <v>63</v>
       </c>
-      <c r="G28" s="27" t="n">
-        <f aca="false">$K$4-E28</f>
+      <c r="G28" s="21" t="n">
+        <f aca="false">ROUND($K$4-E28,4)</f>
         <v>22.5</v>
       </c>
-      <c r="H28" s="27" t="n">
-        <f aca="false">$K$4-F28</f>
+      <c r="H28" s="21" t="n">
+        <f aca="false">ROUND($K$4-F28,4)</f>
         <v>23</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="n">
+      <c r="A29" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="20" t="n">
         <v>46122</v>
       </c>
-      <c r="C29" s="27" t="n">
-        <v>1.6667</v>
-      </c>
-      <c r="D29" s="27" t="n">
+      <c r="C29" s="21" t="n">
+        <v>1.6666666667</v>
+      </c>
+      <c r="D29" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="21" t="n">
         <f aca="false">E28+C29</f>
-        <v>65.1667</v>
-      </c>
-      <c r="F29" s="27" t="n">
+        <v>65.1666666667</v>
+      </c>
+      <c r="F29" s="21" t="n">
         <f aca="false">F28+D29</f>
         <v>65</v>
       </c>
-      <c r="G29" s="27" t="n">
-        <f aca="false">$K$4-E29</f>
+      <c r="G29" s="21" t="n">
+        <f aca="false">ROUND($K$4-E29,4)</f>
         <v>20.8333</v>
       </c>
-      <c r="H29" s="27" t="n">
-        <f aca="false">$K$4-F29</f>
+      <c r="H29" s="21" t="n">
+        <f aca="false">ROUND($K$4-F29,4)</f>
         <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="n">
+      <c r="A30" s="19" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="20" t="n">
         <v>46123</v>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="D30" s="27" t="n">
+      <c r="D30" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="21" t="n">
         <f aca="false">E29+C30</f>
-        <v>66.6667</v>
-      </c>
-      <c r="F30" s="27" t="n">
+        <v>66.6666666667</v>
+      </c>
+      <c r="F30" s="21" t="n">
         <f aca="false">F29+D30</f>
         <v>66.5</v>
       </c>
-      <c r="G30" s="27" t="n">
-        <f aca="false">$K$4-E30</f>
+      <c r="G30" s="21" t="n">
+        <f aca="false">ROUND($K$4-E30,4)</f>
         <v>19.3333</v>
       </c>
-      <c r="H30" s="27" t="n">
-        <f aca="false">$K$4-F30</f>
+      <c r="H30" s="21" t="n">
+        <f aca="false">ROUND($K$4-F30,4)</f>
         <v>19.5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="n">
+      <c r="A31" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="20" t="n">
         <v>46124</v>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="27" t="n">
+      <c r="D31" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="21" t="n">
         <f aca="false">E30+C31</f>
-        <v>66.6667</v>
-      </c>
-      <c r="F31" s="27" t="n">
+        <v>66.6666666667</v>
+      </c>
+      <c r="F31" s="21" t="n">
         <f aca="false">F30+D31</f>
         <v>66.5</v>
       </c>
-      <c r="G31" s="27" t="n">
-        <f aca="false">$K$4-E31</f>
+      <c r="G31" s="21" t="n">
+        <f aca="false">ROUND($K$4-E31,4)</f>
         <v>19.3333</v>
       </c>
-      <c r="H31" s="27" t="n">
-        <f aca="false">$K$4-F31</f>
+      <c r="H31" s="21" t="n">
+        <f aca="false">ROUND($K$4-F31,4)</f>
         <v>19.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="n">
+      <c r="A32" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="20" t="n">
         <v>46125</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="27" t="n">
+      <c r="D32" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="21" t="n">
         <f aca="false">E31+C32</f>
-        <v>66.6667</v>
-      </c>
-      <c r="F32" s="27" t="n">
+        <v>66.6666666667</v>
+      </c>
+      <c r="F32" s="21" t="n">
         <f aca="false">F31+D32</f>
         <v>66.5</v>
       </c>
-      <c r="G32" s="27" t="n">
-        <f aca="false">$K$4-E32</f>
+      <c r="G32" s="21" t="n">
+        <f aca="false">ROUND($K$4-E32,4)</f>
         <v>19.3333</v>
       </c>
-      <c r="H32" s="27" t="n">
-        <f aca="false">$K$4-F32</f>
+      <c r="H32" s="21" t="n">
+        <f aca="false">ROUND($K$4-F32,4)</f>
         <v>19.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="n">
+      <c r="A33" s="19" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="20" t="n">
         <v>46126</v>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="27" t="n">
+      <c r="D33" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="21" t="n">
         <f aca="false">E32+C33</f>
-        <v>66.6667</v>
-      </c>
-      <c r="F33" s="27" t="n">
+        <v>66.6666666667</v>
+      </c>
+      <c r="F33" s="21" t="n">
         <f aca="false">F32+D33</f>
         <v>66.5</v>
       </c>
-      <c r="G33" s="27" t="n">
-        <f aca="false">$K$4-E33</f>
+      <c r="G33" s="21" t="n">
+        <f aca="false">ROUND($K$4-E33,4)</f>
         <v>19.3333</v>
       </c>
-      <c r="H33" s="27" t="n">
-        <f aca="false">$K$4-F33</f>
+      <c r="H33" s="21" t="n">
+        <f aca="false">ROUND($K$4-F33,4)</f>
         <v>19.5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="20" t="n">
         <v>46127</v>
       </c>
-      <c r="C34" s="27" t="n">
-        <v>3.6667</v>
-      </c>
-      <c r="D34" s="27" t="n">
+      <c r="C34" s="21" t="n">
+        <v>3.6666666667</v>
+      </c>
+      <c r="D34" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="21" t="n">
         <f aca="false">E33+C34</f>
-        <v>70.3334</v>
-      </c>
-      <c r="F34" s="27" t="n">
+        <v>70.3333333334</v>
+      </c>
+      <c r="F34" s="21" t="n">
         <f aca="false">F33+D34</f>
         <v>70</v>
       </c>
-      <c r="G34" s="27" t="n">
-        <f aca="false">$K$4-E34</f>
-        <v>15.6666</v>
-      </c>
-      <c r="H34" s="27" t="n">
-        <f aca="false">$K$4-F34</f>
+      <c r="G34" s="21" t="n">
+        <f aca="false">ROUND($K$4-E34,4)</f>
+        <v>15.6667</v>
+      </c>
+      <c r="H34" s="21" t="n">
+        <f aca="false">ROUND($K$4-F34,4)</f>
         <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="20" t="n">
         <v>46128</v>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="D35" s="27" t="n">
+      <c r="D35" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="21" t="n">
         <f aca="false">E34+C35</f>
-        <v>73.8334</v>
-      </c>
-      <c r="F35" s="27" t="n">
+        <v>73.8333333334</v>
+      </c>
+      <c r="F35" s="21" t="n">
         <f aca="false">F34+D35</f>
         <v>73</v>
       </c>
-      <c r="G35" s="27" t="n">
-        <f aca="false">$K$4-E35</f>
-        <v>12.1666</v>
-      </c>
-      <c r="H35" s="27" t="n">
-        <f aca="false">$K$4-F35</f>
+      <c r="G35" s="21" t="n">
+        <f aca="false">ROUND($K$4-E35,4)</f>
+        <v>12.1667</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <f aca="false">ROUND($K$4-F35,4)</f>
         <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="n">
+      <c r="A36" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="20" t="n">
         <v>46129</v>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="D36" s="27" t="n">
+      <c r="D36" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="21" t="n">
         <f aca="false">E35+C36</f>
-        <v>77.3334</v>
-      </c>
-      <c r="F36" s="27" t="n">
+        <v>77.3333333334</v>
+      </c>
+      <c r="F36" s="21" t="n">
         <f aca="false">F35+D36</f>
         <v>76.5</v>
       </c>
-      <c r="G36" s="27" t="n">
-        <f aca="false">$K$4-E36</f>
-        <v>8.66659999999999</v>
-      </c>
-      <c r="H36" s="27" t="n">
-        <f aca="false">$K$4-F36</f>
+      <c r="G36" s="21" t="n">
+        <f aca="false">ROUND($K$4-E36,4)</f>
+        <v>8.6667</v>
+      </c>
+      <c r="H36" s="21" t="n">
+        <f aca="false">ROUND($K$4-F36,4)</f>
         <v>9.5</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="n">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="20" t="n">
         <v>46130</v>
       </c>
-      <c r="C37" s="27" t="n">
-        <v>3.1667</v>
-      </c>
-      <c r="D37" s="27" t="n">
+      <c r="C37" s="21" t="n">
+        <v>3.1666666667</v>
+      </c>
+      <c r="D37" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="21" t="n">
         <f aca="false">E36+C37</f>
-        <v>80.5001</v>
-      </c>
-      <c r="F37" s="27" t="n">
+        <v>80.5000000001</v>
+      </c>
+      <c r="F37" s="21" t="n">
         <f aca="false">F36+D37</f>
         <v>80</v>
       </c>
-      <c r="G37" s="27" t="n">
-        <f aca="false">$K$4-E37</f>
-        <v>5.49989999999998</v>
-      </c>
-      <c r="H37" s="27" t="n">
-        <f aca="false">$K$4-F37</f>
+      <c r="G37" s="21" t="n">
+        <f aca="false">ROUND($K$4-E37,4)</f>
+        <v>5.5</v>
+      </c>
+      <c r="H37" s="21" t="n">
+        <f aca="false">ROUND($K$4-F37,4)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="25" t="n">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="20" t="n">
         <v>46131</v>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="D38" s="27" t="n">
+      <c r="D38" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="21" t="n">
         <f aca="false">E37+C38</f>
-        <v>83.0001</v>
-      </c>
-      <c r="F38" s="27" t="n">
+        <v>83.0000000001</v>
+      </c>
+      <c r="F38" s="21" t="n">
         <f aca="false">F37+D38</f>
         <v>83</v>
       </c>
-      <c r="G38" s="27" t="n">
-        <f aca="false">$K$4-E38</f>
-        <v>2.99989999999998</v>
-      </c>
-      <c r="H38" s="27" t="n">
-        <f aca="false">$K$4-F38</f>
+      <c r="G38" s="21" t="n">
+        <f aca="false">ROUND($K$4-E38,4)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="25" t="n">
+      <c r="H38" s="21" t="n">
+        <f aca="false">ROUND($K$4-F38,4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="26" t="n">
+      <c r="B39" s="20" t="n">
         <v>46132</v>
       </c>
-      <c r="C39" s="27" t="n">
+      <c r="C39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="27" t="n">
+      <c r="D39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="21" t="n">
         <f aca="false">E38+C39</f>
-        <v>84.0001</v>
-      </c>
-      <c r="F39" s="27" t="n">
+        <v>84.0000000001</v>
+      </c>
+      <c r="F39" s="21" t="n">
         <f aca="false">F38+D39</f>
         <v>84</v>
       </c>
-      <c r="G39" s="27" t="n">
-        <f aca="false">$K$4-E39</f>
-        <v>1.99989999999998</v>
-      </c>
-      <c r="H39" s="27" t="n">
-        <f aca="false">$K$4-F39</f>
+      <c r="G39" s="21" t="n">
+        <f aca="false">ROUND($K$4-E39,4)</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="25" t="n">
+      <c r="H39" s="21" t="n">
+        <f aca="false">ROUND($K$4-F39,4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="26" t="n">
+      <c r="B40" s="20" t="n">
         <v>46133</v>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="27" t="n">
+      <c r="D40" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="21" t="n">
         <f aca="false">E39+C40</f>
-        <v>85.0001</v>
-      </c>
-      <c r="F40" s="27" t="n">
+        <v>85.0000000001</v>
+      </c>
+      <c r="F40" s="21" t="n">
         <f aca="false">F39+D40</f>
         <v>85</v>
       </c>
-      <c r="G40" s="27" t="n">
-        <f aca="false">$K$4-E40</f>
-        <v>0.999899999999983</v>
-      </c>
-      <c r="H40" s="27" t="n">
-        <f aca="false">$K$4-F40</f>
+      <c r="G40" s="21" t="n">
+        <f aca="false">ROUND($K$4-E40,4)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="n">
+      <c r="H40" s="21" t="n">
+        <f aca="false">ROUND($K$4-F40,4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="26" t="n">
+      <c r="B41" s="20" t="n">
         <v>46134</v>
       </c>
-      <c r="C41" s="27" t="n">
+      <c r="C41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="27" t="n">
+      <c r="D41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="27" t="n">
+      <c r="E41" s="21" t="n">
         <f aca="false">E40+C41</f>
-        <v>86.0001</v>
-      </c>
-      <c r="F41" s="27" t="n">
+        <v>86.0000000001</v>
+      </c>
+      <c r="F41" s="21" t="n">
         <f aca="false">F40+D41</f>
         <v>86</v>
       </c>
-      <c r="G41" s="27" t="n">
-        <f aca="false">$K$4-E41</f>
-        <v>-0.000100000000017531</v>
-      </c>
-      <c r="H41" s="27" t="n">
-        <f aca="false">$K$4-F41</f>
+      <c r="G41" s="21" t="n">
+        <f aca="false">ROUND($K$4-E41,4)</f>
+        <v>-0</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <f aca="false">ROUND($K$4-F41,4)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
